--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N13_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>109.4427745608287</v>
       </c>
       <c r="E2" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F2" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>88.26008383691615</v>
       </c>
       <c r="E3" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F3" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.00494058425893</v>
+        <v>2.384914488502211</v>
       </c>
       <c r="D4" t="n">
-        <v>59.71033513193549</v>
+        <v>2.951518778637389</v>
       </c>
       <c r="E4" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F4" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>119.9123797652665</v>
+        <v>60.00494058425893</v>
       </c>
       <c r="D5" t="n">
-        <v>119.8729794279197</v>
+        <v>59.71033513193549</v>
       </c>
       <c r="E5" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F5" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.34970488089025</v>
+        <v>119.9123797652665</v>
       </c>
       <c r="D6" t="n">
-        <v>27.7532724824291</v>
+        <v>119.8729794279197</v>
       </c>
       <c r="E6" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F6" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.62060064565285</v>
+        <v>29.34970488089025</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93388746097958</v>
+        <v>27.7532724824291</v>
       </c>
       <c r="E7" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F7" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>70.57246959963942</v>
+        <v>37.62060064565285</v>
       </c>
       <c r="D8" t="n">
-        <v>69.67602845280105</v>
+        <v>35.93388746097958</v>
       </c>
       <c r="E8" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F8" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>59.36989925970356</v>
+        <v>70.57246959963942</v>
       </c>
       <c r="D9" t="n">
-        <v>58.18237012439413</v>
+        <v>69.67602845280105</v>
       </c>
       <c r="E9" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F9" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>87.79756758405129</v>
+        <v>59.36989925970356</v>
       </c>
       <c r="D10" t="n">
-        <v>86.94959420037421</v>
+        <v>58.18237012439413</v>
       </c>
       <c r="E10" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F10" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.58300196976111</v>
+        <v>87.79756758405129</v>
       </c>
       <c r="D11" t="n">
-        <v>28.85677220613702</v>
+        <v>86.94959420037421</v>
       </c>
       <c r="E11" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F11" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.34392670270561</v>
+        <v>28.58300196976111</v>
       </c>
       <c r="D12" t="n">
-        <v>20.78687362135798</v>
+        <v>28.85677220613702</v>
       </c>
       <c r="E12" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F12" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>128.7885375745327</v>
+        <v>20.34392670270561</v>
       </c>
       <c r="D13" t="n">
-        <v>128.699001055433</v>
+        <v>20.78687362135798</v>
       </c>
       <c r="E13" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F13" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.24427326447597</v>
+        <v>128.7885375745327</v>
       </c>
       <c r="D14" t="n">
-        <v>10.74609849928865</v>
+        <v>128.699001055433</v>
       </c>
       <c r="E14" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F14" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>109.1588497157446</v>
+        <v>10.24427326447597</v>
       </c>
       <c r="D15" t="n">
-        <v>109.0520187863315</v>
+        <v>10.74609849928865</v>
       </c>
       <c r="E15" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F15" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>143.3029322242107</v>
+        <v>109.1588497157446</v>
       </c>
       <c r="D16" t="n">
-        <v>143.174753325052</v>
+        <v>109.0520187863315</v>
       </c>
       <c r="E16" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F16" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>110.9832178513011</v>
+        <v>143.3029322242107</v>
       </c>
       <c r="D17" t="n">
-        <v>110.8319587621935</v>
+        <v>143.174753325052</v>
       </c>
       <c r="E17" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F17" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>56.52249441705334</v>
+        <v>110.9832178513011</v>
       </c>
       <c r="D18" t="n">
-        <v>56.317608301643</v>
+        <v>110.8319587621935</v>
       </c>
       <c r="E18" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F18" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>17.10173876282317</v>
+        <v>56.52249441705334</v>
       </c>
       <c r="D19" t="n">
-        <v>16.60181594048512</v>
+        <v>56.317608301643</v>
       </c>
       <c r="E19" t="n">
-        <v>40.82976495868266</v>
+        <v>42.40204682759477</v>
       </c>
       <c r="F19" t="n">
-        <v>40.93038948743425</v>
+        <v>42.42468430287747</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,23 +1056,55 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
+        <v>17.10173876282317</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.60181594048512</v>
+      </c>
+      <c r="E20" t="n">
+        <v>42.40204682759477</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.42468430287747</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>T1791L</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W0035F0001T0006Z000C1N13.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="n">
         <v>33.9707956701056</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>33.50182267799615</v>
       </c>
-      <c r="E20" t="n">
-        <v>40.82976495868266</v>
-      </c>
-      <c r="F20" t="n">
-        <v>40.93038948743425</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>T1791L</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E21" t="n">
+        <v>42.40204682759477</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.42468430287747</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>T1791L</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>109.3766688148786</v>
+        <v>17.77370868241777</v>
       </c>
       <c r="D2" t="n">
-        <v>109.4427745608287</v>
+        <v>17.78445086613466</v>
       </c>
       <c r="E2" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F2" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>88.26074253309125</v>
+        <v>14.34237066162733</v>
       </c>
       <c r="D3" t="n">
-        <v>88.26008383691615</v>
+        <v>14.34226362349887</v>
       </c>
       <c r="E3" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F3" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2.384914488502211</v>
+        <v>0.3875486043816093</v>
       </c>
       <c r="D4" t="n">
-        <v>2.951518778637389</v>
+        <v>0.4796218015285757</v>
       </c>
       <c r="E4" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F4" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.00494058425893</v>
+        <v>9.750802844942077</v>
       </c>
       <c r="D5" t="n">
-        <v>59.71033513193549</v>
+        <v>9.702929458939519</v>
       </c>
       <c r="E5" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F5" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>119.9123797652665</v>
+        <v>19.48576171185581</v>
       </c>
       <c r="D6" t="n">
-        <v>119.8729794279197</v>
+        <v>19.47935915703695</v>
       </c>
       <c r="E6" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F6" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.34970488089025</v>
+        <v>4.769327043144666</v>
       </c>
       <c r="D7" t="n">
-        <v>27.7532724824291</v>
+        <v>4.509906778394729</v>
       </c>
       <c r="E7" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F7" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.62060064565285</v>
+        <v>6.113347604918588</v>
       </c>
       <c r="D8" t="n">
-        <v>35.93388746097958</v>
+        <v>5.839256712409183</v>
       </c>
       <c r="E8" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F8" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>70.57246959963942</v>
+        <v>11.46802630994141</v>
       </c>
       <c r="D9" t="n">
-        <v>69.67602845280105</v>
+        <v>11.32235462358017</v>
       </c>
       <c r="E9" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F9" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.36989925970356</v>
+        <v>9.647608629701828</v>
       </c>
       <c r="D10" t="n">
-        <v>58.18237012439413</v>
+        <v>9.454635145214045</v>
       </c>
       <c r="E10" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F10" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>87.79756758405129</v>
+        <v>14.26710473240834</v>
       </c>
       <c r="D11" t="n">
-        <v>86.94959420037421</v>
+        <v>14.12930905756081</v>
       </c>
       <c r="E11" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F11" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.58300196976111</v>
+        <v>4.64473782008618</v>
       </c>
       <c r="D12" t="n">
-        <v>28.85677220613702</v>
+        <v>4.689225483497265</v>
       </c>
       <c r="E12" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F12" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.34392670270561</v>
+        <v>3.305888089189662</v>
       </c>
       <c r="D13" t="n">
-        <v>20.78687362135798</v>
+        <v>3.377866963470673</v>
       </c>
       <c r="E13" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F13" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>128.7885375745327</v>
+        <v>20.92813735586156</v>
       </c>
       <c r="D14" t="n">
-        <v>128.699001055433</v>
+        <v>20.91358767150787</v>
       </c>
       <c r="E14" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F14" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>10.24427326447597</v>
+        <v>1.664694405477345</v>
       </c>
       <c r="D15" t="n">
-        <v>10.74609849928865</v>
+        <v>1.746241006134406</v>
       </c>
       <c r="E15" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F15" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>109.1588497157446</v>
+        <v>17.7383130788085</v>
       </c>
       <c r="D16" t="n">
-        <v>109.0520187863315</v>
+        <v>17.72095305277888</v>
       </c>
       <c r="E16" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F16" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>143.3029322242107</v>
+        <v>23.28672648643424</v>
       </c>
       <c r="D17" t="n">
-        <v>143.174753325052</v>
+        <v>23.26589741532095</v>
       </c>
       <c r="E17" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F17" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>110.9832178513011</v>
+        <v>18.03477290083644</v>
       </c>
       <c r="D18" t="n">
-        <v>110.8319587621935</v>
+        <v>18.01019329885644</v>
       </c>
       <c r="E18" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F18" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>56.52249441705334</v>
+        <v>9.184905342771168</v>
       </c>
       <c r="D19" t="n">
-        <v>56.317608301643</v>
+        <v>9.151611349016987</v>
       </c>
       <c r="E19" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F19" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>17.10173876282317</v>
+        <v>2.779032548958765</v>
       </c>
       <c r="D20" t="n">
-        <v>16.60181594048512</v>
+        <v>2.697795090328832</v>
       </c>
       <c r="E20" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F20" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>33.9707956701056</v>
+        <v>5.52025429639216</v>
       </c>
       <c r="D21" t="n">
-        <v>33.50182267799615</v>
+        <v>5.444046185174375</v>
       </c>
       <c r="E21" t="n">
-        <v>42.40204682759477</v>
+        <v>6.89033260948415</v>
       </c>
       <c r="F21" t="n">
-        <v>42.42468430287747</v>
+        <v>6.89401119921759</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
